--- a/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
+++ b/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
@@ -491,25 +491,25 @@
   <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОСТАТКИ OZON (КОРОТИЧ) — ДЕНЬГИ В ТОВАРЕ И ПЛАН ЗАРАБОТКА</t>
+          <t>ОСТАТКИ OZON (КОРОТИЧ) — СЕБЕС, ДЕНЬГИ В ТОВАРЕ, ПЛАН ЗАРАБОТКА</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Колонка OZON (Коротич). Себес — по последнему приходу. План маржа/шт — по юнитке (ROI≥30%). Жёлтым — нет себеса (новинки без прихода).</t>
+          <t>Себес новинок = цена инвойса (вон) × 0.064 ₽ × 1,30. План прибыль = 30% от себеса (ROI≥30%). Round Lab Dokdo Toner — 624 ₽ (дано).</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>План маржа ₽/шт</t>
+          <t>План прибыль ROI30 ₽</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>План прибыль ₽</t>
+          <t>Источник себеса</t>
         </is>
       </c>
     </row>
@@ -561,10 +561,12 @@
         <v>3158493</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>139</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>947841</v>
+        <v>947548</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>склад (приход)</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -583,571 +585,853 @@
         <v>9238276</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>199</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>2769284</v>
+        <v>2771483</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>склад (приход)</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE HEARTLEAF BHA PEELING PAD 60PADS</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F7" s="9" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>612</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>734400</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI STARTER KIT</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="5" t="n">
         <v>480</v>
       </c>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F8" s="9" t="n"/>
+      <c r="C8" s="6" t="n">
+        <v>632</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>303360</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>91008</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CELIMAX DUAL BARRIER TRIAL KIT</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="5" t="n">
         <v>448</v>
       </c>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F9" s="9" t="n"/>
+      <c r="C9" s="6" t="n">
+        <v>449</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>201152</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>60346</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI ACNE BUBBLE CLEANSER 155ML</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="5" t="n">
         <v>312</v>
       </c>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F10" s="9" t="n"/>
+      <c r="C10" s="6" t="n">
+        <v>545</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>170040</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>51012</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE FRESH BLACKHEAD JOJOBA CLEANSING OIL 150ML</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="5" t="n">
         <v>315</v>
       </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F11" s="9" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>591</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>186165</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>55849</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI CALMING GLOW PAD 50EA</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="5" t="n">
         <v>984</v>
       </c>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F12" s="9" t="n"/>
+      <c r="C12" s="6" t="n">
+        <v>711</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>699624</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>209887</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL CICA SOOTHING CREAM 50ML</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F13" s="9" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>672</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>806400</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>241920</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL CICA NIACINAMIDE AC CALMING SERUM 40ML</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="5" t="n">
         <v>864</v>
       </c>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F14" s="9" t="n"/>
+      <c r="C14" s="6" t="n">
+        <v>826</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>713664</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>214099</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI ENERGY REPAIR CREAM 50ML</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F15" s="9" t="n"/>
+      <c r="C15" s="6" t="n">
+        <v>960</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>691200</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>207360</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CELIMAX OIL CONTROL MOISTURIZING CREAM 80ML</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F16" s="9" t="n"/>
+      <c r="C16" s="6" t="n">
+        <v>788</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>472800</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>141840</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING KIT</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="5" t="n">
         <v>576</v>
       </c>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F17" s="9" t="n"/>
+      <c r="C17" s="6" t="n">
+        <v>530</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>305280</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>91584</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>CELIMAX ONE STEP BODY BRIGHTENING PAD 60PADS</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="5" t="n">
         <v>528</v>
       </c>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F18" s="9" t="n"/>
+      <c r="C18" s="6" t="n">
+        <v>507</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>267696</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>80309</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE ONE STEP MILD CLEANSING PAD 60PADS</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="5" t="n">
         <v>352</v>
       </c>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F19" s="9" t="n"/>
+      <c r="C19" s="6" t="n">
+        <v>571</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>200992</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>60298</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>CELIMAX DUAL BARRIER MILD GEL CLEANSER 200ML</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="5" t="n">
         <v>288</v>
       </c>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F20" s="9" t="n"/>
+      <c r="C20" s="6" t="n">
+        <v>667</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>192096</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>57629</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI REFRESH CLAY MASK 120G</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="5" t="n">
         <v>408</v>
       </c>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F21" s="9" t="n"/>
+      <c r="C21" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>224400</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>67320</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE GLUTATHIONE LONGLASTING TONE-UP CREAM 35ML</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="5" t="n">
         <v>468</v>
       </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F22" s="9" t="n"/>
+      <c r="C22" s="6" t="n">
+        <v>532</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>248976</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>74693</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE RELIEF MADECICA PH BALANCING FOAM CLEANSING 150ML</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F23" s="9" t="n"/>
+      <c r="C23" s="6" t="n">
+        <v>428</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>136960</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>41088</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>1025 DOKDO BUBBLE FOAM_150ml</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n">
+      <c r="B24" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F24" s="9" t="n"/>
+      <c r="C24" s="6" t="n">
+        <v>595</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>357000</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>107100</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>PINE CALMING CICA CLEANSER_150ml</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F25" s="9" t="n"/>
+      <c r="C25" s="6" t="n">
+        <v>531</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>318600</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>95580</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>PINE CALMING CICA BODY WASH_400ml</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B26" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="9" t="n"/>
+      <c r="C26" s="6" t="n">
+        <v>631</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>252400</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>75720</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>PINE CALMING CICA CREAM PLUS_60ml</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B27" s="5" t="n">
         <v>240</v>
       </c>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F27" s="9" t="n"/>
+      <c r="C27" s="6" t="n">
+        <v>932</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>223680</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>67104</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B28" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F28" s="9" t="n"/>
+      <c r="C28" s="6" t="n">
+        <v>996</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>398400</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>119520</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>PINE CALMING CICA PAD_50pcs</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B29" s="5" t="n">
         <v>270</v>
       </c>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F29" s="9" t="n"/>
+      <c r="C29" s="6" t="n">
+        <v>832</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>224640</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>67392</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>SOYBEAN SERUM_50ml</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B30" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F30" s="9" t="n"/>
+      <c r="C30" s="6" t="n">
+        <v>874</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>183540</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>55062</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>ROUND LAB STICK POUCH KIT</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B31" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F31" s="9" t="n"/>
+      <c r="C31" s="6" t="n">
+        <v>495</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>148500</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>44550</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Ampoule 55ml</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n">
+      <c r="B32" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F32" s="9" t="n"/>
+      <c r="C32" s="6" t="n">
+        <v>674</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1011000</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>303300</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoule 100ml</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B33" s="5" t="n">
         <v>900</v>
       </c>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F33" s="9" t="n"/>
+      <c r="C33" s="6" t="n">
+        <v>865</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>778500</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>233550</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B34" s="5" t="n">
         <v>920</v>
       </c>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F34" s="9" t="n"/>
+      <c r="C34" s="6" t="n">
+        <v>857</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>788440</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>236532</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>PDRN PINK PEPTIDE SERUM 30ml</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
+      <c r="B35" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F35" s="9" t="n"/>
+      <c r="C35" s="6" t="n">
+        <v>882</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>282240</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>84672</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>PDRN PINK EXOSOME SHOT SERUM 7500 30ml</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n">
+      <c r="B36" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F36" s="9" t="n"/>
+      <c r="C36" s="6" t="n">
+        <v>1090</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>436000</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>130800</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>PDRN PINK EXOSOME SHOT SERUM 2000 30ml</t>
         </is>
       </c>
-      <c r="B37" s="8" t="n">
+      <c r="B37" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F37" s="9" t="n"/>
+      <c r="C37" s="6" t="n">
+        <v>990</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>297000</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>89100</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>TXA NIACINAMIDE CAPSULE CREAM 55g</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n">
+      <c r="B38" s="5" t="n">
         <v>240</v>
       </c>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F38" s="9" t="n"/>
+      <c r="C38" s="6" t="n">
+        <v>1206</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>289440</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>86832</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>PDRN PINK COLLAGEN CAPSULE CREAM 55g</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n">
+      <c r="B39" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F39" s="9" t="n"/>
+      <c r="C39" s="6" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>213280</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>63984</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
         </is>
       </c>
-      <c r="B40" s="8" t="n">
+      <c r="B40" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F40" s="9" t="n"/>
+      <c r="C40" s="6" t="n">
+        <v>876</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>175200</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>52560</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>VT REEDLE S LIP PLUMPER EXPERT</t>
         </is>
       </c>
-      <c r="B41" s="8" t="n">
+      <c r="B41" s="5" t="n">
         <v>528</v>
       </c>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F41" s="9" t="n"/>
+      <c r="C41" s="6" t="n">
+        <v>691</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>364848</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>109454</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -1160,122 +1444,180 @@
       </c>
       <c r="C42" s="9" t="n"/>
       <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>НЕТ СЕБЕСА</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>[Derma Factory] PDRN 4% Ampoule</t>
         </is>
       </c>
-      <c r="B43" s="8" t="n">
+      <c r="B43" s="5" t="n">
         <v>1530</v>
       </c>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F43" s="9" t="n"/>
+      <c r="C43" s="6" t="n">
+        <v>532</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>813960</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>244188</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>[Derma Factory] Tranexamic Acid 6% Cream</t>
         </is>
       </c>
-      <c r="B44" s="8" t="n">
+      <c r="B44" s="5" t="n">
         <v>1344</v>
       </c>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F44" s="9" t="n"/>
+      <c r="C44" s="6" t="n">
+        <v>341</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>458304</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>137491</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>[Derma Factory] Retinal 300ppm Cream</t>
         </is>
       </c>
-      <c r="B45" s="8" t="n">
+      <c r="B45" s="5" t="n">
         <v>1248</v>
       </c>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F45" s="9" t="n"/>
+      <c r="C45" s="6" t="n">
+        <v>383</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>477984</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>143395</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>[Derma Factory] Niacinamide 20% Serum</t>
         </is>
       </c>
-      <c r="B46" s="8" t="n">
+      <c r="B46" s="5" t="n">
         <v>1020</v>
       </c>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F46" s="9" t="n"/>
+      <c r="C46" s="6" t="n">
+        <v>229</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>233580</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>70074</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>[Derma Factory] Porphyrin 20% Ampoule stick</t>
         </is>
       </c>
-      <c r="B47" s="8" t="n">
+      <c r="B47" s="5" t="n">
         <v>1053</v>
       </c>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F47" s="9" t="n"/>
+      <c r="C47" s="6" t="n">
+        <v>474</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>499122</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>149737</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>[Derma Factory] Bakuchiol Spicule Cream</t>
         </is>
       </c>
-      <c r="B48" s="8" t="n">
+      <c r="B48" s="5" t="n">
         <v>480</v>
       </c>
-      <c r="C48" s="9" t="n"/>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F48" s="9" t="n"/>
+      <c r="C48" s="6" t="n">
+        <v>395</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>189600</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>56880</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>[Derma Factory] Matrixyl 15% + Argireline 2% Serum</t>
         </is>
       </c>
-      <c r="B49" s="8" t="n">
+      <c r="B49" s="5" t="n">
         <v>420</v>
       </c>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="9" t="n"/>
-      <c r="E49" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F49" s="9" t="n"/>
+      <c r="C49" s="6" t="n">
+        <v>624</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>262080</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>78624</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>инвойс вон×1,3</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -1288,17 +1630,17 @@
       </c>
       <c r="C50" s="12" t="n"/>
       <c r="D50" s="13" t="n">
-        <v>12396768</v>
-      </c>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="13" t="n">
-        <v>3717125</v>
-      </c>
+        <v>28629311</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>8588794</v>
+      </c>
+      <c r="F50" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Остаток: 47,437 шт | Денег в товаре (где есть себес): 12.40 млн ₽ | План прибыли ROI≥30%: 3.72 млн ₽ | Без себеса (новинки): 43 поз.</t>
+          <t>Остаток 47,437 шт | Денег в товаре (себес): 28.63 млн ₽ | План прибыли ROI≥30%: 8.59 млн ₽ | Без себеса: 1 поз (VT eye cream).</t>
         </is>
       </c>
     </row>

--- a/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
+++ b/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
@@ -28,7 +28,7 @@
     <font>
       <b val="1"/>
       <color rgb="00005BFF"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
       <i val="1"/>
@@ -488,28 +488,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОСТАТКИ OZON (КОРОТИЧ) — СЕБЕС, ДЕНЬГИ В ТОВАРЕ, ПЛАН ЗАРАБОТКА</t>
+          <t>ОСТАТКИ OZON (КОРОТИЧ) — СЕБЕС, ДЕНЬГИ В ТОВАРЕ, ПРИБЫЛЬ ПО КАЖДОЙ ПОЗИЦИИ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Себес новинок = цена инвойса (вон) × 0.064 ₽ × 1,30. План прибыль = 30% от себеса (ROI≥30%). Round Lab Dokdo Toner — 624 ₽ (дано).</t>
+          <t>Себес новинок = цена инвойса (вон) × 0.064 × 1,30. Прибыль/шт = 30% от себеса (ROI≥30%). Прибыль всего = прибыль/шт × остаток.</t>
         </is>
       </c>
     </row>
@@ -536,10 +537,15 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>План прибыль ROI30 ₽</t>
+          <t>Прибыль ₽/шт</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Прибыль всего ₽</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Источник себеса</t>
         </is>
@@ -561,9 +567,12 @@
         <v>3158493</v>
       </c>
       <c r="E5" s="6" t="n">
+        <v>139</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>947548</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>склад (приход)</t>
         </is>
@@ -585,9 +594,12 @@
         <v>9238276</v>
       </c>
       <c r="E6" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>2771483</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>склад (приход)</t>
         </is>
@@ -609,9 +621,12 @@
         <v>734400</v>
       </c>
       <c r="E7" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>220320</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -633,9 +648,12 @@
         <v>303360</v>
       </c>
       <c r="E8" s="6" t="n">
+        <v>190</v>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>91008</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -657,9 +675,12 @@
         <v>201152</v>
       </c>
       <c r="E9" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>60346</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -681,9 +702,12 @@
         <v>170040</v>
       </c>
       <c r="E10" s="6" t="n">
+        <v>164</v>
+      </c>
+      <c r="F10" s="6" t="n">
         <v>51012</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -705,9 +729,12 @@
         <v>186165</v>
       </c>
       <c r="E11" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>55849</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -729,9 +756,12 @@
         <v>699624</v>
       </c>
       <c r="E12" s="6" t="n">
+        <v>213</v>
+      </c>
+      <c r="F12" s="6" t="n">
         <v>209887</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -753,9 +783,12 @@
         <v>806400</v>
       </c>
       <c r="E13" s="6" t="n">
+        <v>202</v>
+      </c>
+      <c r="F13" s="6" t="n">
         <v>241920</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -777,9 +810,12 @@
         <v>713664</v>
       </c>
       <c r="E14" s="6" t="n">
+        <v>248</v>
+      </c>
+      <c r="F14" s="6" t="n">
         <v>214099</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -801,9 +837,12 @@
         <v>691200</v>
       </c>
       <c r="E15" s="6" t="n">
+        <v>288</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>207360</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -825,9 +864,12 @@
         <v>472800</v>
       </c>
       <c r="E16" s="6" t="n">
+        <v>236</v>
+      </c>
+      <c r="F16" s="6" t="n">
         <v>141840</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -849,9 +891,12 @@
         <v>305280</v>
       </c>
       <c r="E17" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="F17" s="6" t="n">
         <v>91584</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -873,9 +918,12 @@
         <v>267696</v>
       </c>
       <c r="E18" s="6" t="n">
+        <v>152</v>
+      </c>
+      <c r="F18" s="6" t="n">
         <v>80309</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -897,9 +945,12 @@
         <v>200992</v>
       </c>
       <c r="E19" s="6" t="n">
+        <v>171</v>
+      </c>
+      <c r="F19" s="6" t="n">
         <v>60298</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -921,9 +972,12 @@
         <v>192096</v>
       </c>
       <c r="E20" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" s="6" t="n">
         <v>57629</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -945,9 +999,12 @@
         <v>224400</v>
       </c>
       <c r="E21" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="F21" s="6" t="n">
         <v>67320</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -969,9 +1026,12 @@
         <v>248976</v>
       </c>
       <c r="E22" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="F22" s="6" t="n">
         <v>74693</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -993,9 +1053,12 @@
         <v>136960</v>
       </c>
       <c r="E23" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="F23" s="6" t="n">
         <v>41088</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1017,9 +1080,12 @@
         <v>357000</v>
       </c>
       <c r="E24" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="F24" s="6" t="n">
         <v>107100</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1041,9 +1107,12 @@
         <v>318600</v>
       </c>
       <c r="E25" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="F25" s="6" t="n">
         <v>95580</v>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1065,9 +1134,12 @@
         <v>252400</v>
       </c>
       <c r="E26" s="6" t="n">
+        <v>189</v>
+      </c>
+      <c r="F26" s="6" t="n">
         <v>75720</v>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1089,9 +1161,12 @@
         <v>223680</v>
       </c>
       <c r="E27" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="F27" s="6" t="n">
         <v>67104</v>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1113,9 +1188,12 @@
         <v>398400</v>
       </c>
       <c r="E28" s="6" t="n">
+        <v>299</v>
+      </c>
+      <c r="F28" s="6" t="n">
         <v>119520</v>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1137,9 +1215,12 @@
         <v>224640</v>
       </c>
       <c r="E29" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="F29" s="6" t="n">
         <v>67392</v>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1161,9 +1242,12 @@
         <v>183540</v>
       </c>
       <c r="E30" s="6" t="n">
+        <v>262</v>
+      </c>
+      <c r="F30" s="6" t="n">
         <v>55062</v>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1185,9 +1269,12 @@
         <v>148500</v>
       </c>
       <c r="E31" s="6" t="n">
+        <v>148</v>
+      </c>
+      <c r="F31" s="6" t="n">
         <v>44550</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1209,9 +1296,12 @@
         <v>1011000</v>
       </c>
       <c r="E32" s="6" t="n">
+        <v>202</v>
+      </c>
+      <c r="F32" s="6" t="n">
         <v>303300</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1233,9 +1323,12 @@
         <v>778500</v>
       </c>
       <c r="E33" s="6" t="n">
+        <v>260</v>
+      </c>
+      <c r="F33" s="6" t="n">
         <v>233550</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1257,9 +1350,12 @@
         <v>788440</v>
       </c>
       <c r="E34" s="6" t="n">
+        <v>257</v>
+      </c>
+      <c r="F34" s="6" t="n">
         <v>236532</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1281,9 +1377,12 @@
         <v>282240</v>
       </c>
       <c r="E35" s="6" t="n">
+        <v>265</v>
+      </c>
+      <c r="F35" s="6" t="n">
         <v>84672</v>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1305,9 +1404,12 @@
         <v>436000</v>
       </c>
       <c r="E36" s="6" t="n">
+        <v>327</v>
+      </c>
+      <c r="F36" s="6" t="n">
         <v>130800</v>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1329,9 +1431,12 @@
         <v>297000</v>
       </c>
       <c r="E37" s="6" t="n">
+        <v>297</v>
+      </c>
+      <c r="F37" s="6" t="n">
         <v>89100</v>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1353,9 +1458,12 @@
         <v>289440</v>
       </c>
       <c r="E38" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="F38" s="6" t="n">
         <v>86832</v>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1377,9 +1485,12 @@
         <v>213280</v>
       </c>
       <c r="E39" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="F39" s="6" t="n">
         <v>63984</v>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1401,9 +1512,12 @@
         <v>175200</v>
       </c>
       <c r="E40" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="F40" s="6" t="n">
         <v>52560</v>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1425,9 +1539,12 @@
         <v>364848</v>
       </c>
       <c r="E41" s="6" t="n">
+        <v>207</v>
+      </c>
+      <c r="F41" s="6" t="n">
         <v>109454</v>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1445,7 +1562,8 @@
       <c r="C42" s="9" t="n"/>
       <c r="D42" s="9" t="n"/>
       <c r="E42" s="9" t="n"/>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>НЕТ СЕБЕСА</t>
         </is>
@@ -1467,9 +1585,12 @@
         <v>813960</v>
       </c>
       <c r="E43" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="F43" s="6" t="n">
         <v>244188</v>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1491,9 +1612,12 @@
         <v>458304</v>
       </c>
       <c r="E44" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="F44" s="6" t="n">
         <v>137491</v>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1515,9 +1639,12 @@
         <v>477984</v>
       </c>
       <c r="E45" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="F45" s="6" t="n">
         <v>143395</v>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1539,9 +1666,12 @@
         <v>233580</v>
       </c>
       <c r="E46" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="F46" s="6" t="n">
         <v>70074</v>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1563,9 +1693,12 @@
         <v>499122</v>
       </c>
       <c r="E47" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="F47" s="6" t="n">
         <v>149737</v>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1587,9 +1720,12 @@
         <v>189600</v>
       </c>
       <c r="E48" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="F48" s="6" t="n">
         <v>56880</v>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1611,9 +1747,12 @@
         <v>262080</v>
       </c>
       <c r="E49" s="6" t="n">
+        <v>187</v>
+      </c>
+      <c r="F49" s="6" t="n">
         <v>78624</v>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>инвойс вон×1,3</t>
         </is>
@@ -1630,17 +1769,18 @@
       </c>
       <c r="C50" s="12" t="n"/>
       <c r="D50" s="13" t="n">
-        <v>28629311</v>
-      </c>
-      <c r="E50" s="13" t="n">
+        <v>28629312</v>
+      </c>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="13" t="n">
         <v>8588794</v>
       </c>
-      <c r="F50" s="12" t="n"/>
+      <c r="G50" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Остаток 47,437 шт | Денег в товаре (себес): 28.63 млн ₽ | План прибыли ROI≥30%: 8.59 млн ₽ | Без себеса: 1 поз (VT eye cream).</t>
+          <t>Остаток 47,437 шт | Денег в товаре: 28.63 млн ₽ | Прибыль по всем позициям (ROI≥30%): 8.59 млн ₽ | Без себеса: 1 (VT eye cream).</t>
         </is>
       </c>
     </row>

--- a/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
+++ b/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Себес новинок = цена инвойса (вон) × 0.064 × 1,30. Прибыль/шт = 30% от себеса (ROI≥30%). Прибыль всего = прибыль/шт × остаток.</t>
+          <t>Себес новинок = цена инвойса (вон) × 0.064 × 1,30. Прибыль/шт = 30% от себеса. Celimax тонер 150мл = 828 ₽ (дано).</t>
         </is>
       </c>
     </row>
@@ -588,20 +588,20 @@
         <v>13916</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>664</v>
+        <v>828</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>9238276</v>
+        <v>11522448</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>2771483</v>
+        <v>3456734</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>склад (приход)</t>
+          <t>дано (828)</t>
         </is>
       </c>
     </row>
@@ -1769,18 +1769,18 @@
       </c>
       <c r="C50" s="12" t="n"/>
       <c r="D50" s="13" t="n">
-        <v>28629312</v>
+        <v>30913484</v>
       </c>
       <c r="E50" s="12" t="n"/>
       <c r="F50" s="13" t="n">
-        <v>8588794</v>
+        <v>9274045</v>
       </c>
       <c r="G50" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Остаток 47,437 шт | Денег в товаре: 28.63 млн ₽ | Прибыль по всем позициям (ROI≥30%): 8.59 млн ₽ | Без себеса: 1 (VT eye cream).</t>
+          <t>Остаток 47,437 шт | Денег в товаре: 30.91 млн ₽ | Прибыль по всем (ROI≥30%): 9.27 млн ₽ | Без себеса: 1 (VT eye cream).</t>
         </is>
       </c>
     </row>

--- a/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
+++ b/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Себес новинок = цена инвойса (вон) × 0.064 × 1,30. Прибыль/шт = 30% от себеса. Celimax тонер 150мл = 828 ₽ (дано).</t>
+          <t>Себес новинок = цена инвойса (вон)×0.064×1,30. Прибыль/шт = 30% себеса. Дано вручную: Celimax тонер 828 ₽, Round Lab cleanser 512 ₽, Dokdo toner 624 ₽.</t>
         </is>
       </c>
     </row>
@@ -561,20 +561,20 @@
         <v>6819</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>463</v>
+        <v>512</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>3158493</v>
+        <v>3491328</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>947548</v>
+        <v>1047398</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>склад (приход)</t>
+          <t>дано</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>дано (828)</t>
+          <t>дано</t>
         </is>
       </c>
     </row>
@@ -1769,18 +1769,18 @@
       </c>
       <c r="C50" s="12" t="n"/>
       <c r="D50" s="13" t="n">
-        <v>30913484</v>
+        <v>31246319</v>
       </c>
       <c r="E50" s="12" t="n"/>
       <c r="F50" s="13" t="n">
-        <v>9274045</v>
+        <v>9373895</v>
       </c>
       <c r="G50" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Остаток 47,437 шт | Денег в товаре: 30.91 млн ₽ | Прибыль по всем (ROI≥30%): 9.27 млн ₽ | Без себеса: 1 (VT eye cream).</t>
+          <t>Остаток 47,437 шт | Денег в товаре: 31.25 млн ₽ | Прибыль по всем (ROI≥30%): 9.37 млн ₽ | Без себеса: 1 (VT eye cream).</t>
         </is>
       </c>
     </row>

--- a/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
+++ b/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
@@ -493,7 +493,7 @@
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -503,14 +503,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОСТАТКИ OZON (КОРОТИЧ) — СЕБЕС, ДЕНЬГИ В ТОВАРЕ, ПРИБЫЛЬ ПО КАЖДОЙ ПОЗИЦИИ</t>
+          <t>ОСТАТКИ OZON (КОРОТИЧ) — СЕБЕС (+ФФ 60₽), ДЕНЬГИ В ТОВАРЕ, ПРИБЫЛЬ ПО ПОЗИЦИЯМ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Себес новинок = цена инвойса (вон)×0.064×1,30. Прибыль/шт = 30% себеса. Дано вручную: Celimax тонер 828 ₽, Round Lab cleanser 512 ₽, Dokdo toner 624 ₽.</t>
+          <t>Себес = база + 60 ₽ фулфилмент. Новинки: цена инвойса (вон)×0.064×1,30 + 60. Прибыль/шт = 30% от себеса. Дано: Celimax тонер 828, Round Lab cleanser 512, Dokdo toner 624 (до +ФФ).</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Себес ₽/шт</t>
+          <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -561,20 +561,20 @@
         <v>6819</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>512</v>
+        <v>572</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>3491328</v>
+        <v>3900468</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1047398</v>
+        <v>1170140</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>дано</t>
+          <t>дано +ФФ</t>
         </is>
       </c>
     </row>
@@ -588,20 +588,20 @@
         <v>13916</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>828</v>
+        <v>888</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>11522448</v>
+        <v>12357408</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3456734</v>
+        <v>3707222</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>дано</t>
+          <t>дано +ФФ</t>
         </is>
       </c>
     </row>
@@ -615,20 +615,20 @@
         <v>1200</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>612</v>
+        <v>672</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>734400</v>
+        <v>806400</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>220320</v>
+        <v>241920</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -642,20 +642,20 @@
         <v>480</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>632</v>
+        <v>692</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>303360</v>
+        <v>332160</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>91008</v>
+        <v>99648</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -669,20 +669,20 @@
         <v>448</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>449</v>
+        <v>509</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>201152</v>
+        <v>228032</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>60346</v>
+        <v>68410</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -696,20 +696,20 @@
         <v>312</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>545</v>
+        <v>605</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>170040</v>
+        <v>188760</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>51012</v>
+        <v>56628</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -723,20 +723,20 @@
         <v>315</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>591</v>
+        <v>651</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>186165</v>
+        <v>205065</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>55849</v>
+        <v>61519</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -750,20 +750,20 @@
         <v>984</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>711</v>
+        <v>771</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>699624</v>
+        <v>758664</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>209887</v>
+        <v>227599</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -777,20 +777,20 @@
         <v>1200</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>672</v>
+        <v>732</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>806400</v>
+        <v>878400</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>241920</v>
+        <v>263520</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -804,20 +804,20 @@
         <v>864</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>826</v>
+        <v>886</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>713664</v>
+        <v>765504</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>214099</v>
+        <v>229651</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -831,20 +831,20 @@
         <v>720</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>960</v>
+        <v>1020</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>691200</v>
+        <v>734400</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>207360</v>
+        <v>220320</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -858,20 +858,20 @@
         <v>600</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>788</v>
+        <v>848</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>472800</v>
+        <v>508800</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>141840</v>
+        <v>152640</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -885,20 +885,20 @@
         <v>576</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>530</v>
+        <v>590</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>305280</v>
+        <v>339840</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>91584</v>
+        <v>101952</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -912,20 +912,20 @@
         <v>528</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>507</v>
+        <v>567</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>267696</v>
+        <v>299376</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>80309</v>
+        <v>89813</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -939,20 +939,20 @@
         <v>352</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>571</v>
+        <v>631</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>200992</v>
+        <v>222112</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>60298</v>
+        <v>66634</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -966,20 +966,20 @@
         <v>288</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>667</v>
+        <v>727</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>192096</v>
+        <v>209376</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>57629</v>
+        <v>62813</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -993,20 +993,20 @@
         <v>408</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>550</v>
+        <v>610</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>224400</v>
+        <v>248880</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>67320</v>
+        <v>74664</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1020,20 +1020,20 @@
         <v>468</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>532</v>
+        <v>592</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>248976</v>
+        <v>277056</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>74693</v>
+        <v>83117</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1047,20 +1047,20 @@
         <v>320</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>428</v>
+        <v>488</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>136960</v>
+        <v>156160</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>41088</v>
+        <v>46848</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1074,20 +1074,20 @@
         <v>600</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>595</v>
+        <v>655</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>357000</v>
+        <v>393000</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>107100</v>
+        <v>117900</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1101,20 +1101,20 @@
         <v>600</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>531</v>
+        <v>591</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>318600</v>
+        <v>354600</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>95580</v>
+        <v>106380</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1128,20 +1128,20 @@
         <v>400</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>631</v>
+        <v>691</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>252400</v>
+        <v>276400</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>75720</v>
+        <v>82920</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1155,20 +1155,20 @@
         <v>240</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>932</v>
+        <v>992</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>223680</v>
+        <v>238080</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>67104</v>
+        <v>71424</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1182,20 +1182,20 @@
         <v>400</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>996</v>
+        <v>1056</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>398400</v>
+        <v>422400</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>119520</v>
+        <v>126720</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1209,20 +1209,20 @@
         <v>270</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>832</v>
+        <v>892</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>224640</v>
+        <v>240840</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>67392</v>
+        <v>72252</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1236,20 +1236,20 @@
         <v>210</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>874</v>
+        <v>934</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>183540</v>
+        <v>196140</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>55062</v>
+        <v>58842</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1263,20 +1263,20 @@
         <v>300</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>495</v>
+        <v>555</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>148500</v>
+        <v>166500</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>44550</v>
+        <v>49950</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1290,20 +1290,20 @@
         <v>1500</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>674</v>
+        <v>734</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1011000</v>
+        <v>1101000</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>303300</v>
+        <v>330300</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1317,20 +1317,20 @@
         <v>900</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>865</v>
+        <v>925</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>778500</v>
+        <v>832500</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>233550</v>
+        <v>249750</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1344,20 +1344,20 @@
         <v>920</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>857</v>
+        <v>917</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>788440</v>
+        <v>843640</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>236532</v>
+        <v>253092</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1371,20 +1371,20 @@
         <v>320</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>882</v>
+        <v>942</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>282240</v>
+        <v>301440</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>84672</v>
+        <v>90432</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1398,20 +1398,20 @@
         <v>400</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>1090</v>
+        <v>1150</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>436000</v>
+        <v>460000</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>130800</v>
+        <v>138000</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1425,20 +1425,20 @@
         <v>300</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>990</v>
+        <v>1050</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>297000</v>
+        <v>315000</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>89100</v>
+        <v>94500</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1452,20 +1452,20 @@
         <v>240</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1206</v>
+        <v>1266</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>289440</v>
+        <v>303840</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>86832</v>
+        <v>91152</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1479,20 +1479,20 @@
         <v>160</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>1333</v>
+        <v>1393</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>213280</v>
+        <v>222880</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>63984</v>
+        <v>66864</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1506,20 +1506,20 @@
         <v>200</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>876</v>
+        <v>936</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>175200</v>
+        <v>187200</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>52560</v>
+        <v>56160</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1533,20 +1533,20 @@
         <v>528</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>691</v>
+        <v>751</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>364848</v>
+        <v>396528</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>109454</v>
+        <v>118958</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1579,20 +1579,20 @@
         <v>1530</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>532</v>
+        <v>592</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>813960</v>
+        <v>905760</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>244188</v>
+        <v>271728</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1606,20 +1606,20 @@
         <v>1344</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>341</v>
+        <v>401</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>458304</v>
+        <v>538944</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>137491</v>
+        <v>161683</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1633,20 +1633,20 @@
         <v>1248</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>383</v>
+        <v>443</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>477984</v>
+        <v>552864</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>143395</v>
+        <v>165859</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1660,20 +1660,20 @@
         <v>1020</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>229</v>
+        <v>289</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>233580</v>
+        <v>294780</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>70074</v>
+        <v>88434</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1687,20 +1687,20 @@
         <v>1053</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>474</v>
+        <v>534</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>499122</v>
+        <v>562302</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>149737</v>
+        <v>168691</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1714,20 +1714,20 @@
         <v>480</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>395</v>
+        <v>455</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>189600</v>
+        <v>218400</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>56880</v>
+        <v>65520</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1741,20 +1741,20 @@
         <v>420</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>624</v>
+        <v>684</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>262080</v>
+        <v>287280</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>78624</v>
+        <v>86184</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>инвойс вон×1,3</t>
+          <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
@@ -1769,18 +1769,18 @@
       </c>
       <c r="C50" s="12" t="n"/>
       <c r="D50" s="13" t="n">
-        <v>31246319</v>
+        <v>34029179</v>
       </c>
       <c r="E50" s="12" t="n"/>
       <c r="F50" s="13" t="n">
-        <v>9373895</v>
+        <v>10208753</v>
       </c>
       <c r="G50" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Остаток 47,437 шт | Денег в товаре: 31.25 млн ₽ | Прибыль по всем (ROI≥30%): 9.37 млн ₽ | Без себеса: 1 (VT eye cream).</t>
+          <t>Остаток 47,437 шт | Денег в товаре (с ФФ): 34.03 млн ₽ | Прибыль по всем (ROI≥30%): 10.21 млн ₽ | Без себеса: 1 (VT eye cream).</t>
         </is>
       </c>
     </row>

--- a/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
+++ b/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
@@ -101,26 +101,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -488,64 +494,70 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОСТАТКИ OZON (КОРОТИЧ) — СЕБЕС (+ФФ 60₽), ДЕНЬГИ В ТОВАРЕ, ПРИБЫЛЬ ПО ПОЗИЦИЯМ</t>
+          <t>ОСТАТКИ OZON (КОРОТИЧ) — БАРКОД, СЕБЕС (+ФФ 60₽), ДЕНЬГИ В ТОВАРЕ, ПРИБЫЛЬ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Себес = база + 60 ₽ фулфилмент. Новинки: цена инвойса (вон)×0.064×1,30 + 60. Прибыль/шт = 30% от себеса. Дано: Celimax тонер 828, Round Lab cleanser 512, Dokdo toner 624 (до +ФФ).</t>
+          <t>Себес = база + 60 ₽ ФФ. Новинки: цена инвойса (вон)×0.064×1,30 + 60. Прибыль/шт = 30% себеса. Дано: Celimax тонер 828, Round Lab cleanser 512, Dokdo toner 624 (до +ФФ).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Баркод</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>OZON (Коротич) шт</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Прибыль ₽/шт</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Прибыль всего ₽</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Источник себеса</t>
         </is>
@@ -554,25 +566,30 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>8809738608364</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
           <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>6819</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>572</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>3900468</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>172</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>1170140</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>дано +ФФ</t>
         </is>
@@ -581,25 +598,30 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>8809606850475</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
           <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>13916</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>888</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>12357408</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>266</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>3707222</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>дано +ФФ</t>
         </is>
@@ -608,25 +630,30 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>8809463992615</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX JI WOO GAE HEARTLEAF BHA PEELING PAD 60PADS</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>672</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>806400</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>202</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>241920</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -635,25 +662,30 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>8809971482349</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL NONI STARTER KIT</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>480</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>692</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>332160</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>208</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>99648</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -662,25 +694,30 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>8809606852332</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX DUAL BARRIER TRIAL KIT</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>448</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>509</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>228032</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>153</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>68410</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -689,25 +726,30 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>8809541379468</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL NONI ACNE BUBBLE CLEANSER 155ML</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>312</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>605</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>188760</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>182</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>56628</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -716,25 +758,30 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>8806050298525</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX DERMA NATURE FRESH BLACKHEAD JOJOBA CLEANSING OIL 150ML</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>315</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>651</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>205065</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>195</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>61519</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -743,25 +790,30 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>8809750465464</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL NONI CALMING GLOW PAD 50EA</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>984</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>771</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>758664</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>231</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>227599</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -770,25 +822,30 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>8809782557861</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL CICA SOOTHING CREAM 50ML</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>732</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>878400</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <v>263520</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -797,25 +854,30 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>8809743544626</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL CICA NIACINAMIDE AC CALMING SERUM 40ML</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>864</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>886</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>765504</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>266</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>229651</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -824,25 +886,30 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>8809686386185</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL NONI ENERGY REPAIR CREAM 50ML</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>720</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="D15" s="7" t="n">
         <v>1020</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>734400</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>306</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="7" t="n">
         <v>220320</v>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -851,25 +918,30 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>8809743546880</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX OIL CONTROL MOISTURIZING CREAM 80ML</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="D16" s="7" t="n">
         <v>848</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>508800</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>254</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>152640</v>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -878,25 +950,30 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>8800296551789</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING KIT</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>576</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="D17" s="7" t="n">
         <v>590</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>339840</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>177</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="7" t="n">
         <v>101952</v>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -905,25 +982,30 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>8809463992707</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX ONE STEP BODY BRIGHTENING PAD 60PADS</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="C18" s="6" t="n">
         <v>528</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="D18" s="7" t="n">
         <v>567</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>299376</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>170</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="7" t="n">
         <v>89813</v>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -932,25 +1014,30 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>8809463993889</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX JI WOO GAE ONE STEP MILD CLEANSING PAD 60PADS</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="C19" s="6" t="n">
         <v>352</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="D19" s="7" t="n">
         <v>631</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>222112</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>189</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="7" t="n">
         <v>66634</v>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -959,25 +1046,30 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>8809606850499</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX DUAL BARRIER MILD GEL CLEANSER 200ML</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="C20" s="6" t="n">
         <v>288</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="D20" s="7" t="n">
         <v>727</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>209376</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>218</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="7" t="n">
         <v>62813</v>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -986,25 +1078,30 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>8809954940354</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL NONI REFRESH CLAY MASK 120G</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="C21" s="6" t="n">
         <v>408</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>248880</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>183</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>74664</v>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1013,25 +1110,30 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>8809626564000</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX DERMA NATURE GLUTATHIONE LONGLASTING TONE-UP CREAM 35ML</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="C22" s="6" t="n">
         <v>468</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="D22" s="7" t="n">
         <v>592</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>277056</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>178</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <v>83117</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1040,25 +1142,30 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>8809975194439</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX DERMA NATURE RELIEF MADECICA PH BALANCING FOAM CLEANSING 150ML</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="C23" s="6" t="n">
         <v>320</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="D23" s="7" t="n">
         <v>488</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>156160</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>146</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="7" t="n">
         <v>46848</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1067,25 +1174,30 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>8809738599044</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
           <t>1025 DOKDO BUBBLE FOAM_150ml</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="C24" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="D24" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>393000</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>196</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="7" t="n">
         <v>117900</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1094,25 +1206,30 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>8809864754126</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>PINE CALMING CICA CLEANSER_150ml</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="C25" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="D25" s="7" t="n">
         <v>591</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>354600</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="7" t="n">
         <v>177</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="7" t="n">
         <v>106380</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1121,25 +1238,30 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>8809849802408</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
           <t>PINE CALMING CICA BODY WASH_400ml</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="C26" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="D26" s="7" t="n">
         <v>691</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>276400</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>207</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="7" t="n">
         <v>82920</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1148,25 +1270,30 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>8809962542137</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
           <t>PINE CALMING CICA CREAM PLUS_60ml</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="C27" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="D27" s="7" t="n">
         <v>992</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>238080</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>298</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="7" t="n">
         <v>71424</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1175,25 +1302,30 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>8809962541840</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
           <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="C28" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="D28" s="7" t="n">
         <v>1056</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>422400</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>317</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="7" t="n">
         <v>126720</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1202,25 +1334,30 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>8809750462708</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
           <t>PINE CALMING CICA PAD_50pcs</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="C29" s="6" t="n">
         <v>270</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="D29" s="7" t="n">
         <v>892</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>240840</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>268</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="7" t="n">
         <v>72252</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1229,25 +1366,30 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>8809738593240</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
           <t>SOYBEAN SERUM_50ml</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="C30" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="D30" s="7" t="n">
         <v>934</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>196140</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>280</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="7" t="n">
         <v>58842</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1256,25 +1398,30 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>8809962540553</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
           <t>ROUND LAB STICK POUCH KIT</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="C31" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="D31" s="7" t="n">
         <v>555</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>166500</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>166</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="7" t="n">
         <v>49950</v>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1283,25 +1430,30 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>8809576260601</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
           <t>SKIN1004 Madagascar Centella Ampoule 55ml</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="C32" s="6" t="n">
         <v>1500</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="D32" s="7" t="n">
         <v>734</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>1101000</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="7" t="n">
         <v>330300</v>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1310,25 +1462,30 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>8809576261172</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
           <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoule 100ml</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="C33" s="6" t="n">
         <v>900</v>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="D33" s="7" t="n">
         <v>925</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>832500</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="7" t="n">
         <v>278</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="7" t="n">
         <v>249750</v>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1337,25 +1494,30 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>8809576261134</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
           <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="C34" s="6" t="n">
         <v>920</v>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="D34" s="7" t="n">
         <v>917</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>843640</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="7" t="n">
         <v>275</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="7" t="n">
         <v>253092</v>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1364,25 +1526,30 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t>8800256108053</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
           <t>PDRN PINK PEPTIDE SERUM 30ml</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="C35" s="6" t="n">
         <v>320</v>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="D35" s="7" t="n">
         <v>942</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>301440</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="7" t="n">
         <v>90432</v>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1391,25 +1558,30 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>8800256115549</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
           <t>PDRN PINK EXOSOME SHOT SERUM 7500 30ml</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="C36" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="D36" s="7" t="n">
         <v>1150</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>460000</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="7" t="n">
         <v>345</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="7" t="n">
         <v>138000</v>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1418,25 +1590,30 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>8800256115532</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
           <t>PDRN PINK EXOSOME SHOT SERUM 2000 30ml</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="C37" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="D37" s="7" t="n">
         <v>1050</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="E37" s="7" t="n">
         <v>315000</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="7" t="n">
         <v>315</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="7" t="n">
         <v>94500</v>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1445,25 +1622,30 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>8800256119660</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
           <t>TXA NIACINAMIDE CAPSULE CREAM 55g</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="C38" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="D38" s="7" t="n">
         <v>1266</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>303840</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="7" t="n">
         <v>380</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="7" t="n">
         <v>91152</v>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1472,25 +1654,30 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
+          <t>8800256118885</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
           <t>PDRN PINK COLLAGEN CAPSULE CREAM 55g</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="C39" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="D39" s="7" t="n">
         <v>1393</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="E39" s="7" t="n">
         <v>222880</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="7" t="n">
         <v>418</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="7" t="n">
         <v>66864</v>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1499,25 +1686,30 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>8800256113101</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
           <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="C40" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="C40" s="6" t="n">
+      <c r="D40" s="7" t="n">
         <v>936</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>187200</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="7" t="n">
         <v>281</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="7" t="n">
         <v>56160</v>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1526,44 +1718,54 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>8803463006501</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
           <t>VT REEDLE S LIP PLUMPER EXPERT</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="C41" s="6" t="n">
         <v>528</v>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="D41" s="7" t="n">
         <v>751</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="E41" s="7" t="n">
         <v>396528</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="7" t="n">
         <v>225</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="7" t="n">
         <v>118958</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>8809695679544</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>VT REEDLE SHOT LIFTING EYE CREAM</t>
         </is>
       </c>
-      <c r="B42" s="8" t="n">
+      <c r="C42" s="10" t="n">
         <v>1056</v>
       </c>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>НЕТ СЕБЕСА</t>
         </is>
@@ -1572,25 +1774,30 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
+          <t>8809331319360</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] PDRN 4% Ampoule</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="C43" s="6" t="n">
         <v>1530</v>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="D43" s="7" t="n">
         <v>592</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="E43" s="7" t="n">
         <v>905760</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="7" t="n">
         <v>178</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="7" t="n">
         <v>271728</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1599,25 +1806,30 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
+          <t>8809563068258</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Tranexamic Acid 6% Cream</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="C44" s="6" t="n">
         <v>1344</v>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="D44" s="7" t="n">
         <v>401</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>538944</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="7" t="n">
         <v>161683</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1626,25 +1838,30 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t>8809563066773</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Retinal 300ppm Cream</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="C45" s="6" t="n">
         <v>1248</v>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="D45" s="7" t="n">
         <v>443</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>552864</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="7" t="n">
         <v>133</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="7" t="n">
         <v>165859</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1653,25 +1870,30 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t>8809563066797</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Niacinamide 20% Serum</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="C46" s="6" t="n">
         <v>1020</v>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="D46" s="7" t="n">
         <v>289</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>294780</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="F46" s="7" t="n">
         <v>87</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="G46" s="7" t="n">
         <v>88434</v>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1680,25 +1902,30 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>8809563067923</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Porphyrin 20% Ampoule stick</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="C47" s="6" t="n">
         <v>1053</v>
       </c>
-      <c r="C47" s="6" t="n">
+      <c r="D47" s="7" t="n">
         <v>534</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>562302</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="F47" s="7" t="n">
         <v>160</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="G47" s="7" t="n">
         <v>168691</v>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1707,25 +1934,30 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t>8809331313818</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Bakuchiol Spicule Cream</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="C48" s="6" t="n">
         <v>480</v>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="D48" s="7" t="n">
         <v>455</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>218400</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="F48" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="G48" s="7" t="n">
         <v>65520</v>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1734,51 +1966,57 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>8809331317182</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Matrixyl 15% + Argireline 2% Serum</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="C49" s="6" t="n">
         <v>420</v>
       </c>
-      <c r="C49" s="6" t="n">
+      <c r="D49" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="E49" s="7" t="n">
         <v>287280</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="F49" s="7" t="n">
         <v>205</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="G49" s="7" t="n">
         <v>86184</v>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="12" t="n"/>
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B50" s="11" t="n">
+      <c r="C50" s="14" t="n">
         <v>47437</v>
       </c>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="15" t="n">
         <v>34029179</v>
       </c>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="13" t="n">
+      <c r="F50" s="12" t="n"/>
+      <c r="G50" s="15" t="n">
         <v>10208753</v>
       </c>
-      <c r="G50" s="12" t="n"/>
+      <c r="H50" s="12" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="14" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Остаток 47,437 шт | Денег в товаре (с ФФ): 34.03 млн ₽ | Прибыль по всем (ROI≥30%): 10.21 млн ₽ | Без себеса: 1 (VT eye cream).</t>
         </is>

--- a/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
+++ b/outputs/остатки_OZON_Коротич_с_себесом_план.xlsx
@@ -109,21 +109,29 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -494,23 +502,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОСТАТКИ OZON (КОРОТИЧ) — БАРКОД, СЕБЕС (+ФФ 60₽), ДЕНЬГИ В ТОВАРЕ, ПРИБЫЛЬ</t>
+          <t>ОСТАТКИ OZON (КОРОТИЧ) — БРЕНД, КАТЕГОРИЯ, СЕБЕС (+ФФ 60₽), ДЕНЬГИ, ПРИБЫЛЬ</t>
         </is>
       </c>
     </row>
@@ -529,35 +539,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Бренд</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Категория (для чего)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>OZON (Коротич) шт</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Себес+ФФ ₽/шт</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Сумма себес ₽</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Прибыль ₽/шт</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Прибыль всего ₽</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Источник себеса</t>
         </is>
@@ -571,25 +591,35 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Пенка для умывания</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>6819</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="F5" s="7" t="n">
         <v>572</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="G5" s="7" t="n">
         <v>3900468</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="H5" s="7" t="n">
         <v>172</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="I5" s="7" t="n">
         <v>1170140</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>дано +ФФ</t>
         </is>
@@ -603,25 +633,35 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Тонер</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
           <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>13916</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="F6" s="7" t="n">
         <v>888</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="G6" s="7" t="n">
         <v>12357408</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="H6" s="7" t="n">
         <v>266</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="I6" s="7" t="n">
         <v>3707222</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>дано +ФФ</t>
         </is>
@@ -635,25 +675,35 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Пэды</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX JI WOO GAE HEARTLEAF BHA PEELING PAD 60PADS</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="E7" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="F7" s="7" t="n">
         <v>672</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="G7" s="7" t="n">
         <v>806400</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="H7" s="7" t="n">
         <v>202</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="I7" s="7" t="n">
         <v>241920</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -667,25 +717,35 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL NONI STARTER KIT</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>480</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="F8" s="7" t="n">
         <v>692</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="G8" s="7" t="n">
         <v>332160</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="H8" s="7" t="n">
         <v>208</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="I8" s="7" t="n">
         <v>99648</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -699,25 +759,35 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX DUAL BARRIER TRIAL KIT</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>448</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="F9" s="7" t="n">
         <v>509</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="G9" s="7" t="n">
         <v>228032</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="H9" s="7" t="n">
         <v>153</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="I9" s="7" t="n">
         <v>68410</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -731,25 +801,35 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Пенка для умывания</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL NONI ACNE BUBBLE CLEANSER 155ML</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="E10" s="6" t="n">
         <v>312</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="F10" s="7" t="n">
         <v>605</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="G10" s="7" t="n">
         <v>188760</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="H10" s="7" t="n">
         <v>182</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="I10" s="7" t="n">
         <v>56628</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -763,25 +843,35 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Гидрофильное масло</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX DERMA NATURE FRESH BLACKHEAD JOJOBA CLEANSING OIL 150ML</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>315</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="F11" s="7" t="n">
         <v>651</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="G11" s="7" t="n">
         <v>205065</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="H11" s="7" t="n">
         <v>195</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="I11" s="7" t="n">
         <v>61519</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -795,25 +885,35 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Пэды</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL NONI CALMING GLOW PAD 50EA</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="E12" s="6" t="n">
         <v>984</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="F12" s="7" t="n">
         <v>771</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="G12" s="7" t="n">
         <v>758664</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="H12" s="7" t="n">
         <v>231</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="I12" s="7" t="n">
         <v>227599</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -827,25 +927,35 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL CICA SOOTHING CREAM 50ML</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="E13" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="F13" s="7" t="n">
         <v>732</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="G13" s="7" t="n">
         <v>878400</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="H13" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="I13" s="7" t="n">
         <v>263520</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -859,25 +969,35 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Сыворотка</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL CICA NIACINAMIDE AC CALMING SERUM 40ML</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>864</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="F14" s="7" t="n">
         <v>886</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>765504</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="H14" s="7" t="n">
         <v>266</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="I14" s="7" t="n">
         <v>229651</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -891,25 +1011,35 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL NONI ENERGY REPAIR CREAM 50ML</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="E15" s="6" t="n">
         <v>720</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="F15" s="7" t="n">
         <v>1020</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>734400</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>306</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="I15" s="7" t="n">
         <v>220320</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -923,25 +1053,35 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX OIL CONTROL MOISTURIZING CREAM 80ML</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="E16" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="F16" s="7" t="n">
         <v>848</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="G16" s="7" t="n">
         <v>508800</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="H16" s="7" t="n">
         <v>254</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="I16" s="7" t="n">
         <v>152640</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -955,25 +1095,35 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING KIT</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>576</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="F17" s="7" t="n">
         <v>590</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>339840</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="H17" s="7" t="n">
         <v>177</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="I17" s="7" t="n">
         <v>101952</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -987,25 +1137,35 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Пэды для тела</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX ONE STEP BODY BRIGHTENING PAD 60PADS</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="E18" s="6" t="n">
         <v>528</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="F18" s="7" t="n">
         <v>567</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="G18" s="7" t="n">
         <v>299376</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="H18" s="7" t="n">
         <v>170</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="I18" s="7" t="n">
         <v>89813</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1019,25 +1179,35 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Пэды</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX JI WOO GAE ONE STEP MILD CLEANSING PAD 60PADS</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="E19" s="6" t="n">
         <v>352</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="F19" s="7" t="n">
         <v>631</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="G19" s="7" t="n">
         <v>222112</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="H19" s="7" t="n">
         <v>189</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="I19" s="7" t="n">
         <v>66634</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1051,25 +1221,35 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Гель для умывания</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX DUAL BARRIER MILD GEL CLEANSER 200ML</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="E20" s="6" t="n">
         <v>288</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="F20" s="7" t="n">
         <v>727</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="G20" s="7" t="n">
         <v>209376</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="H20" s="7" t="n">
         <v>218</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="I20" s="7" t="n">
         <v>62813</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1083,25 +1263,35 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Маска для лица</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX THE REAL NONI REFRESH CLAY MASK 120G</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="E21" s="6" t="n">
         <v>408</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="F21" s="7" t="n">
         <v>610</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="G21" s="7" t="n">
         <v>248880</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="H21" s="7" t="n">
         <v>183</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="I21" s="7" t="n">
         <v>74664</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1115,25 +1305,35 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX DERMA NATURE GLUTATHIONE LONGLASTING TONE-UP CREAM 35ML</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="E22" s="6" t="n">
         <v>468</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="F22" s="7" t="n">
         <v>592</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="G22" s="7" t="n">
         <v>277056</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="H22" s="7" t="n">
         <v>178</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="I22" s="7" t="n">
         <v>83117</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1147,25 +1347,35 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Пенка для умывания</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
           <t>CELIMAX DERMA NATURE RELIEF MADECICA PH BALANCING FOAM CLEANSING 150ML</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>320</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="F23" s="7" t="n">
         <v>488</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="G23" s="7" t="n">
         <v>156160</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="H23" s="7" t="n">
         <v>146</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="I23" s="7" t="n">
         <v>46848</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1179,25 +1389,35 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Пенка для умывания</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
           <t>1025 DOKDO BUBBLE FOAM_150ml</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="E24" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="F24" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="G24" s="7" t="n">
         <v>393000</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="H24" s="7" t="n">
         <v>196</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="I24" s="7" t="n">
         <v>117900</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1211,25 +1431,35 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Пенка для умывания</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
           <t>PINE CALMING CICA CLEANSER_150ml</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="E25" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="F25" s="7" t="n">
         <v>591</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="G25" s="7" t="n">
         <v>354600</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="H25" s="7" t="n">
         <v>177</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="I25" s="7" t="n">
         <v>106380</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1243,25 +1473,35 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Гель для душа</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
           <t>PINE CALMING CICA BODY WASH_400ml</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="F26" s="7" t="n">
         <v>691</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="G26" s="7" t="n">
         <v>276400</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="H26" s="7" t="n">
         <v>207</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="I26" s="7" t="n">
         <v>82920</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1275,25 +1515,35 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
           <t>PINE CALMING CICA CREAM PLUS_60ml</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="E27" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="F27" s="7" t="n">
         <v>992</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="G27" s="7" t="n">
         <v>238080</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="H27" s="7" t="n">
         <v>298</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="I27" s="7" t="n">
         <v>71424</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1307,25 +1557,35 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
           <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="E28" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="F28" s="7" t="n">
         <v>1056</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="G28" s="7" t="n">
         <v>422400</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="H28" s="7" t="n">
         <v>317</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="I28" s="7" t="n">
         <v>126720</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1339,25 +1599,35 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Пэды</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
           <t>PINE CALMING CICA PAD_50pcs</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="E29" s="6" t="n">
         <v>270</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="F29" s="7" t="n">
         <v>892</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="G29" s="7" t="n">
         <v>240840</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="H29" s="7" t="n">
         <v>268</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="I29" s="7" t="n">
         <v>72252</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1371,25 +1641,35 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Сыворотка</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
           <t>SOYBEAN SERUM_50ml</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="E30" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="F30" s="7" t="n">
         <v>934</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="G30" s="7" t="n">
         <v>196140</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="H30" s="7" t="n">
         <v>280</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="I30" s="7" t="n">
         <v>58842</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1403,25 +1683,35 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Набор</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
           <t>ROUND LAB STICK POUCH KIT</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="E31" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="F31" s="7" t="n">
         <v>555</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="G31" s="7" t="n">
         <v>166500</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="H31" s="7" t="n">
         <v>166</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="I31" s="7" t="n">
         <v>49950</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1435,25 +1725,35 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Сыворотка</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
           <t>SKIN1004 Madagascar Centella Ampoule 55ml</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="E32" s="6" t="n">
         <v>1500</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="F32" s="7" t="n">
         <v>734</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="G32" s="7" t="n">
         <v>1101000</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="H32" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="I32" s="7" t="n">
         <v>330300</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1467,25 +1767,35 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Сыворотка</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
           <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoule 100ml</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="E33" s="6" t="n">
         <v>900</v>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="F33" s="7" t="n">
         <v>925</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="G33" s="7" t="n">
         <v>832500</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="H33" s="7" t="n">
         <v>278</v>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="I33" s="7" t="n">
         <v>249750</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1499,25 +1809,35 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
           <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="E34" s="6" t="n">
         <v>920</v>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="F34" s="7" t="n">
         <v>917</v>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="G34" s="7" t="n">
         <v>843640</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="H34" s="7" t="n">
         <v>275</v>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="I34" s="7" t="n">
         <v>253092</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1531,25 +1851,35 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
+          <t>MEDICUBE</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Сыворотка</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
           <t>PDRN PINK PEPTIDE SERUM 30ml</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="E35" s="6" t="n">
         <v>320</v>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="F35" s="7" t="n">
         <v>942</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="G35" s="7" t="n">
         <v>301440</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="H35" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="I35" s="7" t="n">
         <v>90432</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1563,25 +1893,35 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
+          <t>MEDICUBE</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Сыворотка</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
           <t>PDRN PINK EXOSOME SHOT SERUM 7500 30ml</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="E36" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="F36" s="7" t="n">
         <v>1150</v>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="G36" s="7" t="n">
         <v>460000</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="H36" s="7" t="n">
         <v>345</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="I36" s="7" t="n">
         <v>138000</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1595,25 +1935,35 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
+          <t>MEDICUBE</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Сыворотка</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
           <t>PDRN PINK EXOSOME SHOT SERUM 2000 30ml</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="E37" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="F37" s="7" t="n">
         <v>1050</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="G37" s="7" t="n">
         <v>315000</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="H37" s="7" t="n">
         <v>315</v>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="I37" s="7" t="n">
         <v>94500</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1627,25 +1977,35 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
+          <t>MEDICUBE</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
           <t>TXA NIACINAMIDE CAPSULE CREAM 55g</t>
         </is>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="E38" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="F38" s="7" t="n">
         <v>1266</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="G38" s="7" t="n">
         <v>303840</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="H38" s="7" t="n">
         <v>380</v>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="I38" s="7" t="n">
         <v>91152</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1659,25 +2019,35 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
+          <t>MEDICUBE</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
           <t>PDRN PINK COLLAGEN CAPSULE CREAM 55g</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="E39" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="F39" s="7" t="n">
         <v>1393</v>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="G39" s="7" t="n">
         <v>222880</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="H39" s="7" t="n">
         <v>418</v>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="I39" s="7" t="n">
         <v>66864</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1691,25 +2061,35 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
+          <t>MEDICUBE</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
           <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
         </is>
       </c>
-      <c r="C40" s="6" t="n">
+      <c r="E40" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="F40" s="7" t="n">
         <v>936</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="G40" s="7" t="n">
         <v>187200</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="H40" s="7" t="n">
         <v>281</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="I40" s="7" t="n">
         <v>56160</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1723,25 +2103,35 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
+          <t>VT COSMETIC</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Средство для губ</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
           <t>VT REEDLE S LIP PLUMPER EXPERT</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="E41" s="6" t="n">
         <v>528</v>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="F41" s="7" t="n">
         <v>751</v>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="G41" s="7" t="n">
         <v>396528</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="H41" s="7" t="n">
         <v>225</v>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="I41" s="7" t="n">
         <v>118958</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1755,17 +2145,27 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
+          <t>VT COSMETIC</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Крем для глаз</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT LIFTING EYE CREAM</t>
         </is>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="E42" s="10" t="n">
         <v>1056</v>
       </c>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
       <c r="F42" s="11" t="n"/>
       <c r="G42" s="11" t="n"/>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>НЕТ СЕБЕСА</t>
         </is>
@@ -1779,25 +2179,35 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
+          <t>DERMA FACTORY</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Сыворотка</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] PDRN 4% Ampoule</t>
         </is>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="E43" s="6" t="n">
         <v>1530</v>
       </c>
-      <c r="D43" s="7" t="n">
+      <c r="F43" s="7" t="n">
         <v>592</v>
       </c>
-      <c r="E43" s="7" t="n">
+      <c r="G43" s="7" t="n">
         <v>905760</v>
       </c>
-      <c r="F43" s="7" t="n">
+      <c r="H43" s="7" t="n">
         <v>178</v>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="I43" s="7" t="n">
         <v>271728</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1811,25 +2221,35 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
+          <t>DERMA FACTORY</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Tranexamic Acid 6% Cream</t>
         </is>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="E44" s="6" t="n">
         <v>1344</v>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="F44" s="7" t="n">
         <v>401</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="G44" s="7" t="n">
         <v>538944</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="H44" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="I44" s="7" t="n">
         <v>161683</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1843,25 +2263,35 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
+          <t>DERMA FACTORY</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Retinal 300ppm Cream</t>
         </is>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="E45" s="6" t="n">
         <v>1248</v>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="F45" s="7" t="n">
         <v>443</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="G45" s="7" t="n">
         <v>552864</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="H45" s="7" t="n">
         <v>133</v>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="I45" s="7" t="n">
         <v>165859</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1875,25 +2305,35 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
+          <t>DERMA FACTORY</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Сыворотка</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Niacinamide 20% Serum</t>
         </is>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="E46" s="6" t="n">
         <v>1020</v>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="F46" s="7" t="n">
         <v>289</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="G46" s="7" t="n">
         <v>294780</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="H46" s="7" t="n">
         <v>87</v>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="I46" s="7" t="n">
         <v>88434</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1907,25 +2347,35 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
+          <t>DERMA FACTORY</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Стик для лица</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Porphyrin 20% Ampoule stick</t>
         </is>
       </c>
-      <c r="C47" s="6" t="n">
+      <c r="E47" s="6" t="n">
         <v>1053</v>
       </c>
-      <c r="D47" s="7" t="n">
+      <c r="F47" s="7" t="n">
         <v>534</v>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="G47" s="7" t="n">
         <v>562302</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="H47" s="7" t="n">
         <v>160</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="I47" s="7" t="n">
         <v>168691</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1939,25 +2389,35 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
+          <t>DERMA FACTORY</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Крем для лица</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Bakuchiol Spicule Cream</t>
         </is>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="E48" s="6" t="n">
         <v>480</v>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="F48" s="7" t="n">
         <v>455</v>
       </c>
-      <c r="E48" s="7" t="n">
+      <c r="G48" s="7" t="n">
         <v>218400</v>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="H48" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="I48" s="7" t="n">
         <v>65520</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1971,25 +2431,35 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
+          <t>DERMA FACTORY</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Сыворотка</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
           <t>[Derma Factory] Matrixyl 15% + Argireline 2% Serum</t>
         </is>
       </c>
-      <c r="C49" s="6" t="n">
+      <c r="E49" s="6" t="n">
         <v>420</v>
       </c>
-      <c r="D49" s="7" t="n">
+      <c r="F49" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="E49" s="7" t="n">
+      <c r="G49" s="7" t="n">
         <v>287280</v>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="H49" s="7" t="n">
         <v>205</v>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="I49" s="7" t="n">
         <v>86184</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>инвойс×1,3 +ФФ</t>
         </is>
@@ -1997,23 +2467,25 @@
     </row>
     <row r="50">
       <c r="A50" s="12" t="n"/>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C50" s="14" t="n">
+      <c r="E50" s="14" t="n">
         <v>47437</v>
-      </c>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="15" t="n">
-        <v>34029179</v>
       </c>
       <c r="F50" s="12" t="n"/>
       <c r="G50" s="15" t="n">
+        <v>34029179</v>
+      </c>
+      <c r="H50" s="12" t="n"/>
+      <c r="I50" s="15" t="n">
         <v>10208753</v>
       </c>
-      <c r="H50" s="12" t="n"/>
+      <c r="J50" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
